--- a/RWS05.xlsx
+++ b/RWS05.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="131">
   <si>
     <t/>
   </si>
@@ -386,12 +386,6 @@
   </si>
   <si>
     <t>MAGNUM MINI CMP 6S</t>
-  </si>
-  <si>
-    <t>20138340</t>
-  </si>
-  <si>
-    <t>WALLS POPLRE PARTYPK</t>
   </si>
   <si>
     <t>20140183</t>
@@ -802,7 +796,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F58"/>
+  <dimension ref="A1:F57"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1927,7 +1921,7 @@
         <v>32</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>19</v>
@@ -1944,33 +1938,13 @@
         <v>3</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>32</v>
+        <v>129</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="B58" s="1" t="s">
         <v>130</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="E58" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F58" s="1" t="s">
-        <v>132</v>
       </c>
     </row>
   </sheetData>
